--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.60977581785043</v>
+        <v>2.861588570400695</v>
       </c>
       <c r="D2" t="n">
-        <v>14.6124304706733</v>
+        <v>2.374519951484411</v>
       </c>
       <c r="E2" t="n">
-        <v>9.392235728213643</v>
+        <v>1.526238305834717</v>
       </c>
       <c r="F2" t="n">
-        <v>9.686140447808196</v>
+        <v>1.573997822768832</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.15128196422443</v>
+        <v>3.112083319186469</v>
       </c>
       <c r="D3" t="n">
-        <v>18.69577892299434</v>
+        <v>3.038064074986579</v>
       </c>
       <c r="E3" t="n">
-        <v>9.392235728213643</v>
+        <v>1.526238305834717</v>
       </c>
       <c r="F3" t="n">
-        <v>9.686140447808196</v>
+        <v>1.573997822768832</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.97153872421995</v>
+        <v>2.432875042685742</v>
       </c>
       <c r="D4" t="n">
-        <v>12.13511156734927</v>
+        <v>1.971955629694257</v>
       </c>
       <c r="E4" t="n">
-        <v>9.392235728213643</v>
+        <v>1.526238305834717</v>
       </c>
       <c r="F4" t="n">
-        <v>9.686140447808196</v>
+        <v>1.573997822768832</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.35271334213846</v>
+        <v>6.7198159180975</v>
       </c>
       <c r="D5" t="n">
-        <v>41.26408219573653</v>
+        <v>6.705413356807187</v>
       </c>
       <c r="E5" t="n">
-        <v>9.392235728213643</v>
+        <v>1.526238305834717</v>
       </c>
       <c r="F5" t="n">
-        <v>9.686140447808196</v>
+        <v>1.573997822768832</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.70210392399943</v>
+        <v>2.389091887649907</v>
       </c>
       <c r="D6" t="n">
-        <v>14.7904471687767</v>
+        <v>2.403447664926214</v>
       </c>
       <c r="E6" t="n">
-        <v>9.392235728213643</v>
+        <v>1.526238305834717</v>
       </c>
       <c r="F6" t="n">
-        <v>9.686140447808196</v>
+        <v>1.573997822768832</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.769449194698801</v>
+        <v>1.100035494138555</v>
       </c>
       <c r="D7" t="n">
-        <v>6.791702249145112</v>
+        <v>1.103651615486081</v>
       </c>
       <c r="E7" t="n">
-        <v>9.392235728213643</v>
+        <v>1.526238305834717</v>
       </c>
       <c r="F7" t="n">
-        <v>9.686140447808196</v>
+        <v>1.573997822768832</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.71327129584424</v>
+        <v>2.715906585574689</v>
       </c>
       <c r="D8" t="n">
-        <v>16.45620779053252</v>
+        <v>2.674133765961534</v>
       </c>
       <c r="E8" t="n">
-        <v>9.392235728213643</v>
+        <v>1.526238305834717</v>
       </c>
       <c r="F8" t="n">
-        <v>9.686140447808196</v>
+        <v>1.573997822768832</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.89670632705584</v>
+        <v>3.720714778146574</v>
       </c>
       <c r="D9" t="n">
-        <v>23.15648520412642</v>
+        <v>3.762928845670543</v>
       </c>
       <c r="E9" t="n">
-        <v>9.392235728213643</v>
+        <v>1.526238305834717</v>
       </c>
       <c r="F9" t="n">
-        <v>9.686140447808196</v>
+        <v>1.573997822768832</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
